--- a/data/regression.xlsx
+++ b/data/regression.xlsx
@@ -3,11 +3,10 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -17,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>ACTION</t>
   </si>
@@ -37,6 +36,105 @@
     <t>CHECK</t>
   </si>
   <si>
+    <t xml:space="preserve">VALUE 3</t>
+  </si>
+  <si>
+    <t>sql</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT psword FROM users WHERE id = 4</t>
+  </si>
+  <si>
+    <t>"[^"]*":"([^"]+)"</t>
+  </si>
+  <si>
+    <t>getVariable</t>
+  </si>
+  <si>
+    <t>sqlPassword</t>
+  </si>
+  <si>
+    <t>powershell</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">$a = "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${sqlPassword}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">$b = "sauce"</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>$c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = $a + "_" + $b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">echo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>$c</t>
+    </r>
+  </si>
+  <si>
+    <t>^.*$</t>
+  </si>
+  <si>
+    <t>webPassword</t>
+  </si>
+  <si>
     <t>web</t>
   </si>
   <si>
@@ -61,7 +159,7 @@
     <t>#password</t>
   </si>
   <si>
-    <t>secret_sauce</t>
+    <t>${webPassword}</t>
   </si>
   <si>
     <t>clickButton</t>
@@ -79,29 +177,160 @@
     <t>https://www.saucedemo.com/inventory.html/</t>
   </si>
   <si>
-    <t>powershell</t>
-  </si>
-  <si>
     <t>Get-Date</t>
   </si>
   <si>
     <t>contains</t>
   </si>
   <si>
-    <t xml:space="preserve">echo Hello</t>
-  </si>
-  <si>
-    <t>Hello</t>
+    <t>runps1</t>
+  </si>
+  <si>
+    <t>./data/scripts/demoScript.ps1</t>
+  </si>
+  <si>
+    <t>./data/assertions/demoAssertion.xlsx</t>
+  </si>
+  <si>
+    <t>softAssertions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">echo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="2"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PROD</t>
+    </r>
+  </si>
+  <si>
+    <t>PROD</t>
   </si>
   <si>
     <t>equals</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SELECT * FROM users WHERE [user] = '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="2"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>david</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'</t>
+    </r>
+  </si>
+  <si>
+    <t>"user":"david"</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SELECT [user] FROM users WHERE psword = '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${sqlPassword}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">$d = "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${webPassword}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> === " +</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> $c</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">echo $d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secret_sauce === secret_sauce</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -116,13 +345,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11.000000"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11.000000"/>
       <color theme="10"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11.000000"/>
+      <color indexed="2"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -135,8 +381,32 @@
         <bgColor indexed="26"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor theme="7" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor theme="8" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor theme="6" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -159,19 +429,67 @@
       </bottom>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" applyNumberFormat="0" applyFont="0" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="22">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+    <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="2" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="2" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="3" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="4" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="2" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="2" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="5" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -673,11 +991,12 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="43.140625"/>
-    <col customWidth="1" min="2" max="2" width="33.00390625"/>
+    <col customWidth="1" min="2" max="2" width="54.421875"/>
     <col customWidth="1" min="3" max="3" width="45.28125"/>
     <col customWidth="1" min="4" max="4" width="45.8515625"/>
-    <col customWidth="1" min="5" max="5" width="24.140625"/>
+    <col customWidth="1" min="5" max="5" width="48.00390625"/>
     <col customWidth="1" min="6" max="6" width="23.00390625"/>
+    <col customWidth="1" min="7" max="7" width="23.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -699,303 +1018,308 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="G6" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3"/>
-    </row>
-    <row r="4" ht="14.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" ht="14.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" ht="14.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" ht="14.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="2"/>
-      <c r="F7"/>
-    </row>
-    <row r="8" ht="14.25">
-      <c r="A8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8">
+      <c r="B13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="15">
         <v>2026</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25">
-      <c r="A9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="F13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="16"/>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="19"/>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="9"/>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="C2"/>
-    <hyperlink r:id="rId2" ref="C7"/>
+    <hyperlink r:id="rId1" ref="C7"/>
+    <hyperlink r:id="rId2" ref="C12"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="43.140625"/>
-    <col customWidth="1" min="2" max="2" width="33.00390625"/>
-    <col customWidth="1" min="3" max="3" width="45.28125"/>
-    <col customWidth="1" min="4" max="4" width="45.8515625"/>
-    <col customWidth="1" min="5" max="5" width="24.140625"/>
-    <col customWidth="1" min="6" max="6" width="23.00390625"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3"/>
-    </row>
-    <row r="4" ht="14.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" ht="14.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" ht="14.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" ht="14.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="2"/>
-      <c r="F7"/>
-    </row>
-    <row r="8" ht="14.25">
-      <c r="A8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8">
-        <v>2026</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25">
-      <c r="A9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="C2"/>
-    <hyperlink r:id="rId2" ref="C7"/>
-  </hyperlinks>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
 </file>